--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Task.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4924" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4904" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -442,7 +442,7 @@
 </t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
+    <t>Erweiterungen für die Aufgabe, die durch url unterschieden werden.</t>
   </si>
   <si>
     <t>closed</t>
@@ -471,6 +471,10 @@
     <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Task.extension:acceptDate</t>
   </si>
   <si>
@@ -571,9 +575,6 @@
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
@@ -597,10 +598,6 @@
     <t>Die Task-Ressource enthält zwei Kennungen. Die erste ist die Kennung für den Task, die ein E-Rezept darstellt. Die andere Kennung repräsentiert den Patienten als Eigentümer des E-Rezepts via Krankenversichertennummer (KVNR)</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Request.identifier, Event.identifier</t>
   </si>
   <si>
@@ -608,9 +605,6 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
   </si>
   <si>
     <t>Task.identifier:PrescriptionID</t>
@@ -626,7 +620,7 @@
     <t>E-Rezept-ID</t>
   </si>
   <si>
-    <t>Die E-Rezept-ID ist der Hauptidentifikator für die Task Ressource und den gesamten E-Rezept Workflow. Dieser Identifikator wird vom E-Rezept Fachdienst generiert und darf nicht manuell geändert werden.</t>
+    <t>Die E-Rezept-ID ist der Hauptidentifikator für die Task Ressource und den gesamten E-Rezept Workflow. Dieser Identifikator wird vom E-Rezept-Fachdienst generiert und darf nicht manuell geändert werden.</t>
   </si>
   <si>
     <t>Task.identifier:AccessCode</t>
@@ -638,7 +632,7 @@
     <t>AccessCode Identifier</t>
   </si>
   <si>
-    <t>Generiert vom E-Rezept Fachdienst. Dieser Identifikator muss in jeder Anfrage zur Task Ressource übertragen werden.</t>
+    <t>Generiert vom E-Rezept-Fachdienst. Dieser Identifikator muss in jeder Anfrage zur Task Ressource übertragen werden.</t>
   </si>
   <si>
     <t>Task.identifier:AccessCode.id</t>
@@ -675,6 +669,12 @@
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -824,15 +824,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -863,10 +855,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -896,9 +884,6 @@
     <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Enables a formal definition of how he task is to be performed, enabling automation.</t>
   </si>
   <si>
@@ -912,9 +897,6 @@
   </si>
   <si>
     <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Enables a formal definition of how he task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
@@ -936,9 +918,6 @@
     <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, ServiceRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a task is created to fulfill a procedureRequest ( = FocusOn ) to collect a specimen from a patient.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Request.basedOn, Event.basedOn</t>
   </si>
   <si>
@@ -1033,9 +1012,6 @@
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
     <t>Task.businessStatus</t>
   </si>
   <si>
@@ -1043,9 +1019,6 @@
   </si>
   <si>
     <t>Contains business-specific nuances of the business state.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>There's often a need to track substates of a task - this is often variable by specific workflow implementation.</t>
@@ -1152,9 +1125,6 @@
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.text</t>
@@ -1333,9 +1303,6 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
-    <t>DR</t>
-  </si>
-  <si>
     <t>Task.authoredOn</t>
   </si>
   <si>
@@ -1630,9 +1597,6 @@
   </si>
   <si>
     <t>Free-text information captured about the task as it progresses.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note, Event.note</t>
@@ -2603,7 +2567,7 @@
     <col min="37" max="37" width="47.7734375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="94.296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3730,7 +3694,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -3750,13 +3714,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>78</v>
@@ -3778,13 +3742,13 @@
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3844,7 +3808,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3864,13 +3828,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>78</v>
@@ -3892,13 +3856,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3958,7 +3922,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>140</v>
@@ -3978,13 +3942,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>78</v>
@@ -4006,13 +3970,13 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -4072,7 +4036,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>140</v>
@@ -4092,13 +4056,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>78</v>
@@ -4120,13 +4084,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4186,7 +4150,7 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>140</v>
@@ -4206,13 +4170,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>78</v>
@@ -4234,13 +4198,13 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4300,7 +4264,7 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>140</v>
@@ -4320,14 +4284,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4349,16 +4313,16 @@
         <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -4395,16 +4359,16 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>178</v>
@@ -4528,33 +4492,33 @@
         <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AN17" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>78</v>
@@ -4576,13 +4540,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4642,33 +4606,33 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AN18" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4693,10 +4657,10 @@
         <v>180</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4756,30 +4720,30 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AN19" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4802,13 +4766,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4859,7 +4823,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4877,7 +4841,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4888,14 +4852,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4917,13 +4881,13 @@
         <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4964,13 +4928,13 @@
         <v>136</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>210</v>
@@ -4991,7 +4955,7 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
@@ -5214,7 +5178,7 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
@@ -5376,7 +5340,7 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>247</v>
@@ -5498,9 +5462,7 @@
       <c r="M26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5549,39 +5511,39 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5604,16 +5566,16 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5663,42 +5625,42 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>78</v>
@@ -5720,10 +5682,10 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
         <v>182</v>
@@ -5786,30 +5748,30 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AN28" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5832,19 +5794,17 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5893,7 +5853,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5908,10 +5868,10 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5922,10 +5882,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5951,16 +5911,14 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -6009,7 +5967,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -6024,10 +5982,10 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -6038,10 +5996,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6064,17 +6022,15 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6123,7 +6079,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6132,16 +6088,16 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -6152,10 +6108,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6181,14 +6137,14 @@
         <v>180</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -6237,7 +6193,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6246,30 +6202,30 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6292,19 +6248,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6353,7 +6309,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6362,16 +6318,16 @@
         <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6382,10 +6338,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6411,14 +6367,14 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -6446,10 +6402,10 @@
         <v>217</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -6467,7 +6423,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -6482,13 +6438,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -6496,10 +6452,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6525,13 +6481,13 @@
         <v>224</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6557,10 +6513,10 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>78</v>
@@ -6581,7 +6537,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6590,7 +6546,7 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>100</v>
@@ -6599,21 +6555,21 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6639,16 +6595,14 @@
         <v>224</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6673,10 +6627,10 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>78</v>
@@ -6697,7 +6651,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6706,7 +6660,7 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
@@ -6715,21 +6669,21 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6755,13 +6709,13 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6769,7 +6723,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6790,10 +6744,10 @@
         <v>217</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -6811,7 +6765,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6826,13 +6780,13 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6840,10 +6794,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6869,20 +6823,20 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q38" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="R38" t="s" s="2">
         <v>78</v>
@@ -6906,10 +6860,10 @@
         <v>217</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6927,7 +6881,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6942,13 +6896,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6956,10 +6910,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6985,13 +6939,13 @@
         <v>224</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7017,13 +6971,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -7041,7 +6995,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7050,30 +7004,30 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7096,17 +7050,15 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7155,7 +7107,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7173,7 +7125,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -7184,10 +7136,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7210,19 +7162,19 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -7271,7 +7223,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7280,19 +7232,19 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -7300,14 +7252,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7326,19 +7278,17 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7387,7 +7337,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7396,19 +7346,19 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -7416,10 +7366,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7442,13 +7392,13 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7499,7 +7449,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7517,7 +7467,7 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7528,14 +7478,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7557,13 +7507,13 @@
         <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7604,13 +7554,13 @@
         <v>136</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>210</v>
@@ -7631,7 +7581,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7642,10 +7592,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7668,16 +7618,16 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7727,7 +7677,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7736,7 +7686,7 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>100</v>
@@ -7756,10 +7706,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7785,13 +7735,13 @@
         <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7820,10 +7770,10 @@
         <v>229</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7841,7 +7791,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7870,10 +7820,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7896,16 +7846,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7955,7 +7905,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7964,7 +7914,7 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>100</v>
@@ -7973,21 +7923,21 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8010,16 +7960,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8069,7 +8019,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8098,10 +8048,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8124,19 +8074,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -8185,7 +8133,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8194,19 +8142,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -8214,10 +8162,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8243,14 +8191,12 @@
         <v>256</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8299,7 +8245,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8308,34 +8254,34 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>261</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8354,17 +8300,17 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8413,7 +8359,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8422,19 +8368,19 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8442,14 +8388,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8468,17 +8414,17 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="M52" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8527,7 +8473,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8536,7 +8482,7 @@
         <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>100</v>
@@ -8545,7 +8491,7 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8556,10 +8502,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8582,19 +8528,17 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8643,7 +8587,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8652,19 +8596,19 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8672,10 +8616,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8701,16 +8645,14 @@
         <v>224</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8738,10 +8680,10 @@
         <v>112</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8759,7 +8701,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8768,30 +8710,30 @@
         <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8814,13 +8756,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8871,7 +8813,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8889,7 +8831,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8900,14 +8842,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8929,13 +8871,13 @@
         <v>133</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8976,13 +8918,13 @@
         <v>136</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>210</v>
@@ -9003,7 +8945,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -9014,10 +8956,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9040,19 +8982,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -9081,7 +9023,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -9099,7 +9041,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9108,7 +9050,7 @@
         <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
@@ -9117,21 +9059,21 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9154,19 +9096,19 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9215,7 +9157,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9233,25 +9175,25 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9270,19 +9212,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9331,7 +9273,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9340,19 +9282,19 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9360,10 +9302,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9386,19 +9328,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9447,7 +9387,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9456,19 +9396,19 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9476,10 +9416,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9505,13 +9445,13 @@
         <v>224</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9537,10 +9477,10 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9561,7 +9501,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9570,30 +9510,30 @@
         <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>502</v>
+        <v>492</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9616,16 +9556,16 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9675,7 +9615,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9684,19 +9624,19 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9704,10 +9644,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9730,17 +9670,15 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9789,7 +9727,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9798,30 +9736,30 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>514</v>
+        <v>504</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9844,17 +9782,15 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9903,7 +9839,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9912,34 +9848,34 @@
         <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9958,16 +9894,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10017,7 +9953,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10026,16 +9962,16 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -10046,10 +9982,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10072,17 +10008,17 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -10131,7 +10067,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10140,7 +10076,7 @@
         <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>100</v>
@@ -10149,7 +10085,7 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -10160,10 +10096,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10186,13 +10122,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10243,7 +10179,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10261,7 +10197,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -10272,14 +10208,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10301,13 +10237,13 @@
         <v>133</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10345,16 +10281,16 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>210</v>
@@ -10375,7 +10311,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -10386,14 +10322,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10415,16 +10351,16 @@
         <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10473,7 +10409,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10502,10 +10438,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10528,17 +10464,17 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10587,7 +10523,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10605,7 +10541,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10616,10 +10552,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10645,16 +10581,16 @@
         <v>256</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10703,7 +10639,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10712,30 +10648,30 @@
         <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>261</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10758,17 +10694,15 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10817,7 +10751,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10826,16 +10760,16 @@
         <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10846,14 +10780,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10872,17 +10806,17 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10919,7 +10853,7 @@
         <v>78</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="AC73" s="2"/>
       <c r="AD73" t="s" s="2">
@@ -10929,7 +10863,7 @@
         <v>138</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10938,7 +10872,7 @@
         <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>100</v>
@@ -10947,7 +10881,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10958,10 +10892,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10984,13 +10918,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11041,7 +10975,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11059,7 +10993,7 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -11070,14 +11004,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11099,13 +11033,13 @@
         <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11143,16 +11077,16 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>210</v>
@@ -11173,7 +11107,7 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -11184,14 +11118,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11213,16 +11147,16 @@
         <v>133</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11271,7 +11205,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11300,14 +11234,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11329,16 +11263,16 @@
         <v>224</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11363,10 +11297,10 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>78</v>
@@ -11387,7 +11321,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>88</v>
@@ -11396,7 +11330,7 @@
         <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>100</v>
@@ -11405,21 +11339,21 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11442,13 +11376,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11499,7 +11433,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>88</v>
@@ -11508,7 +11442,7 @@
         <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>100</v>
@@ -11517,7 +11451,7 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
@@ -11528,16 +11462,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11556,17 +11490,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11615,7 +11549,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11624,7 +11558,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>100</v>
@@ -11633,7 +11567,7 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
@@ -11644,10 +11578,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11670,13 +11604,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11727,7 +11661,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11745,7 +11679,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11756,14 +11690,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11785,13 +11719,13 @@
         <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11829,16 +11763,16 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>210</v>
@@ -11859,7 +11793,7 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11870,14 +11804,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11899,16 +11833,16 @@
         <v>133</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11957,7 +11891,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11986,14 +11920,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12015,16 +11949,16 @@
         <v>224</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12049,10 +11983,10 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
@@ -12073,7 +12007,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>88</v>
@@ -12082,7 +12016,7 @@
         <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>100</v>
@@ -12091,21 +12025,21 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12128,13 +12062,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12185,7 +12119,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12203,7 +12137,7 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -12214,14 +12148,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12243,13 +12177,13 @@
         <v>133</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12290,13 +12224,13 @@
         <v>136</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>210</v>
@@ -12317,7 +12251,7 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12328,10 +12262,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12354,19 +12288,19 @@
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12395,7 +12329,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -12413,7 +12347,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12422,7 +12356,7 @@
         <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>100</v>
@@ -12431,21 +12365,21 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12468,13 +12402,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12525,7 +12459,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12543,7 +12477,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12554,14 +12488,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12583,13 +12517,13 @@
         <v>133</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12630,13 +12564,13 @@
         <v>136</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>210</v>
@@ -12657,7 +12591,7 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12668,10 +12602,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12697,16 +12631,16 @@
         <v>102</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12755,7 +12689,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12773,21 +12707,21 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>608</v>
+        <v>597</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12810,16 +12744,16 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12869,7 +12803,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12887,21 +12821,21 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12927,14 +12861,14 @@
         <v>108</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12983,7 +12917,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13001,21 +12935,21 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>624</v>
+        <v>613</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13038,19 +12972,17 @@
         <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13099,7 +13031,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13117,21 +13049,21 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>632</v>
+        <v>621</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13154,19 +13086,19 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13215,7 +13147,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13233,21 +13165,21 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>642</v>
+        <v>631</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13270,19 +13202,19 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13331,7 +13263,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13349,21 +13281,21 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13386,13 +13318,13 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13443,7 +13375,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>88</v>
@@ -13452,7 +13384,7 @@
         <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>100</v>
@@ -13461,7 +13393,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13472,16 +13404,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13500,17 +13432,17 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13559,7 +13491,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13568,7 +13500,7 @@
         <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>100</v>
@@ -13577,7 +13509,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13588,10 +13520,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13614,13 +13546,13 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13671,7 +13603,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13689,7 +13621,7 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13700,14 +13632,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13729,13 +13661,13 @@
         <v>133</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13773,16 +13705,16 @@
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>210</v>
@@ -13803,7 +13735,7 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13814,14 +13746,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13843,16 +13775,16 @@
         <v>133</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13901,7 +13833,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13930,14 +13862,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -13959,16 +13891,16 @@
         <v>224</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13993,10 +13925,10 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="Z100" t="s" s="2">
         <v>78</v>
@@ -14017,7 +13949,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>88</v>
@@ -14026,7 +13958,7 @@
         <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>100</v>
@@ -14035,21 +13967,21 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14072,13 +14004,13 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14129,7 +14061,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14147,7 +14079,7 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -14158,14 +14090,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14187,13 +14119,13 @@
         <v>133</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14234,13 +14166,13 @@
         <v>136</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>210</v>
@@ -14261,7 +14193,7 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14272,10 +14204,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14298,19 +14230,19 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14339,7 +14271,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14357,7 +14289,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14366,7 +14298,7 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>100</v>
@@ -14375,21 +14307,21 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14412,13 +14344,13 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14469,7 +14401,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14487,7 +14419,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14498,14 +14430,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14527,13 +14459,13 @@
         <v>133</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14574,13 +14506,13 @@
         <v>136</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>210</v>
@@ -14601,7 +14533,7 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14612,10 +14544,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14641,16 +14573,16 @@
         <v>102</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -14699,7 +14631,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14717,21 +14649,21 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>608</v>
+        <v>597</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14754,16 +14686,16 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14813,7 +14745,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14831,21 +14763,21 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14871,21 +14803,21 @@
         <v>108</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -14927,7 +14859,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14945,21 +14877,21 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>624</v>
+        <v>613</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14982,19 +14914,17 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -15043,7 +14973,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15061,21 +14991,21 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>632</v>
+        <v>621</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15098,19 +15028,19 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -15159,7 +15089,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15177,21 +15107,21 @@
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>642</v>
+        <v>631</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15214,19 +15144,19 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15275,7 +15205,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15293,21 +15223,21 @@
         <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15330,16 +15260,16 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15389,7 +15319,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>88</v>
@@ -15398,7 +15328,7 @@
         <v>88</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>100</v>
@@ -15407,7 +15337,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15418,10 +15348,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15444,17 +15374,17 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15491,7 +15421,7 @@
         <v>78</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="AC113" s="2"/>
       <c r="AD113" t="s" s="2">
@@ -15501,7 +15431,7 @@
         <v>138</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15510,7 +15440,7 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>100</v>
@@ -15519,7 +15449,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15530,10 +15460,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15556,13 +15486,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15613,7 +15543,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15631,7 +15561,7 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -15642,14 +15572,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15671,13 +15601,13 @@
         <v>133</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15715,16 +15645,16 @@
         <v>78</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>210</v>
@@ -15745,7 +15675,7 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
@@ -15756,14 +15686,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15785,16 +15715,16 @@
         <v>133</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -15843,7 +15773,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15872,14 +15802,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15901,16 +15831,14 @@
         <v>224</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15935,10 +15863,10 @@
         <v>78</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="Z117" t="s" s="2">
         <v>78</v>
@@ -15959,7 +15887,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>88</v>
@@ -15968,7 +15896,7 @@
         <v>88</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>100</v>
@@ -15977,21 +15905,21 @@
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16014,17 +15942,17 @@
         <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>78</v>
@@ -16073,7 +16001,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>88</v>
@@ -16082,7 +16010,7 @@
         <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>100</v>
@@ -16091,7 +16019,7 @@
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>78</v>
@@ -16102,13 +16030,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>78</v>
@@ -16130,17 +16058,17 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16189,7 +16117,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16198,7 +16126,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>100</v>
@@ -16207,7 +16135,7 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>78</v>
@@ -16218,10 +16146,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16244,13 +16172,13 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16301,7 +16229,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16319,7 +16247,7 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -16330,14 +16258,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -16359,13 +16287,13 @@
         <v>133</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16403,16 +16331,16 @@
         <v>78</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
         <v>210</v>
@@ -16433,7 +16361,7 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16444,14 +16372,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16473,16 +16401,16 @@
         <v>133</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16531,7 +16459,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16560,14 +16488,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16589,16 +16517,14 @@
         <v>224</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16623,10 +16549,10 @@
         <v>78</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="Z123" t="s" s="2">
         <v>78</v>
@@ -16647,7 +16573,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>88</v>
@@ -16656,7 +16582,7 @@
         <v>88</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>100</v>
@@ -16665,21 +16591,21 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16702,13 +16628,13 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16759,7 +16685,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16777,7 +16703,7 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -16788,14 +16714,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16817,13 +16743,13 @@
         <v>133</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16864,13 +16790,13 @@
         <v>136</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF125" t="s" s="2">
         <v>210</v>
@@ -16891,7 +16817,7 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
@@ -16902,10 +16828,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16928,19 +16854,19 @@
         <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16969,7 +16895,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>78</v>
@@ -16987,7 +16913,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16996,7 +16922,7 @@
         <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
@@ -17005,21 +16931,21 @@
         <v>78</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17042,13 +16968,13 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17099,7 +17025,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17117,7 +17043,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -17128,14 +17054,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17157,13 +17083,13 @@
         <v>133</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17204,13 +17130,13 @@
         <v>136</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AF128" t="s" s="2">
         <v>210</v>
@@ -17231,7 +17157,7 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>78</v>
@@ -17242,10 +17168,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17271,16 +17197,16 @@
         <v>102</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -17329,7 +17255,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17347,21 +17273,21 @@
         <v>78</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>608</v>
+        <v>597</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17384,16 +17310,16 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17443,7 +17369,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17461,21 +17387,21 @@
         <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17501,21 +17427,21 @@
         <v>108</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>78</v>
@@ -17557,7 +17483,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17575,21 +17501,21 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>624</v>
+        <v>613</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17612,19 +17538,17 @@
         <v>89</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17673,7 +17597,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17691,21 +17615,21 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>632</v>
+        <v>621</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17728,19 +17652,19 @@
         <v>89</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -17789,7 +17713,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17807,21 +17731,21 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>642</v>
+        <v>631</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17844,19 +17768,19 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -17905,7 +17829,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17923,21 +17847,21 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17960,17 +17884,17 @@
         <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18019,7 +17943,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>88</v>
@@ -18028,7 +17952,7 @@
         <v>88</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>100</v>
@@ -18037,7 +17961,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
